--- a/artfynd/A 49930-2025 artfynd.xlsx
+++ b/artfynd/A 49930-2025 artfynd.xlsx
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129084138</v>
+        <v>129084143</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>82897</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>782588</v>
+        <v>782726</v>
       </c>
       <c r="R6" t="n">
-        <v>7291928</v>
+        <v>7292092</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129084143</v>
+        <v>129084138</v>
       </c>
       <c r="B7" t="n">
-        <v>82897</v>
+        <v>98651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782726</v>
+        <v>782588</v>
       </c>
       <c r="R7" t="n">
-        <v>7292092</v>
+        <v>7291928</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 49930-2025 artfynd.xlsx
+++ b/artfynd/A 49930-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129084141</v>
       </c>
       <c r="B2" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129084134</v>
       </c>
       <c r="B3" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129084129</v>
       </c>
       <c r="B4" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129084143</v>
+        <v>129084138</v>
       </c>
       <c r="B6" t="n">
-        <v>82897</v>
+        <v>98656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>782726</v>
+        <v>782588</v>
       </c>
       <c r="R6" t="n">
-        <v>7292092</v>
+        <v>7291928</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129084138</v>
+        <v>129084143</v>
       </c>
       <c r="B7" t="n">
-        <v>98651</v>
+        <v>82897</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782588</v>
+        <v>782726</v>
       </c>
       <c r="R7" t="n">
-        <v>7291928</v>
+        <v>7292092</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1260,7 +1260,7 @@
         <v>129084131</v>
       </c>
       <c r="B8" t="n">
-        <v>90552</v>
+        <v>90555</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129084139</v>
       </c>
       <c r="B9" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129084136</v>
       </c>
       <c r="B11" t="n">
-        <v>92279</v>
+        <v>92284</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 49930-2025 artfynd.xlsx
+++ b/artfynd/A 49930-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129084141</v>
       </c>
       <c r="B2" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129084134</v>
       </c>
       <c r="B3" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129084129</v>
       </c>
       <c r="B4" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129084138</v>
       </c>
       <c r="B6" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129084143</v>
       </c>
       <c r="B7" t="n">
-        <v>82897</v>
+        <v>82898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129084131</v>
       </c>
       <c r="B8" t="n">
-        <v>90555</v>
+        <v>90558</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129084139</v>
       </c>
       <c r="B9" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129084142</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129084136</v>
       </c>
       <c r="B11" t="n">
-        <v>92284</v>
+        <v>92287</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 49930-2025 artfynd.xlsx
+++ b/artfynd/A 49930-2025 artfynd.xlsx
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129084138</v>
+        <v>129084143</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>82898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>782588</v>
+        <v>782726</v>
       </c>
       <c r="R6" t="n">
-        <v>7291928</v>
+        <v>7292092</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129084143</v>
+        <v>129084138</v>
       </c>
       <c r="B7" t="n">
-        <v>82898</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782726</v>
+        <v>782588</v>
       </c>
       <c r="R7" t="n">
-        <v>7292092</v>
+        <v>7291928</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 49930-2025 artfynd.xlsx
+++ b/artfynd/A 49930-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129084129</v>
+        <v>129084140</v>
       </c>
       <c r="B4" t="n">
-        <v>91491</v>
+        <v>56904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>782583</v>
+        <v>782641</v>
       </c>
       <c r="R4" t="n">
-        <v>7291821</v>
+        <v>7291986</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129084140</v>
+        <v>129084129</v>
       </c>
       <c r="B5" t="n">
-        <v>56904</v>
+        <v>91491</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>782641</v>
+        <v>782583</v>
       </c>
       <c r="R5" t="n">
-        <v>7291986</v>
+        <v>7291821</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 49930-2025 artfynd.xlsx
+++ b/artfynd/A 49930-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129084141</v>
       </c>
       <c r="B2" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129084134</v>
       </c>
       <c r="B3" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129084140</v>
+        <v>129084129</v>
       </c>
       <c r="B4" t="n">
-        <v>56904</v>
+        <v>91497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>782641</v>
+        <v>782583</v>
       </c>
       <c r="R4" t="n">
-        <v>7291986</v>
+        <v>7291821</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129084129</v>
+        <v>129084140</v>
       </c>
       <c r="B5" t="n">
-        <v>91491</v>
+        <v>56906</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>782583</v>
+        <v>782641</v>
       </c>
       <c r="R5" t="n">
-        <v>7291821</v>
+        <v>7291986</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129084143</v>
+        <v>129084138</v>
       </c>
       <c r="B6" t="n">
-        <v>82898</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>782726</v>
+        <v>782588</v>
       </c>
       <c r="R6" t="n">
-        <v>7292092</v>
+        <v>7291928</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129084138</v>
+        <v>129084143</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>82902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782588</v>
+        <v>782726</v>
       </c>
       <c r="R7" t="n">
-        <v>7291928</v>
+        <v>7292092</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1260,7 +1260,7 @@
         <v>129084131</v>
       </c>
       <c r="B8" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129084139</v>
       </c>
       <c r="B9" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129084142</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129084136</v>
       </c>
       <c r="B11" t="n">
-        <v>92287</v>
+        <v>92294</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 49930-2025 artfynd.xlsx
+++ b/artfynd/A 49930-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129084141</v>
       </c>
       <c r="B2" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129084134</v>
       </c>
       <c r="B3" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129084129</v>
+        <v>129084140</v>
       </c>
       <c r="B4" t="n">
-        <v>91497</v>
+        <v>56906</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>782583</v>
+        <v>782641</v>
       </c>
       <c r="R4" t="n">
-        <v>7291821</v>
+        <v>7291986</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129084140</v>
+        <v>129084129</v>
       </c>
       <c r="B5" t="n">
-        <v>56906</v>
+        <v>91504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>782641</v>
+        <v>782583</v>
       </c>
       <c r="R5" t="n">
-        <v>7291986</v>
+        <v>7291821</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
         <v>129084138</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129084143</v>
       </c>
       <c r="B7" t="n">
-        <v>82902</v>
+        <v>82871</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129084131</v>
       </c>
       <c r="B8" t="n">
-        <v>90562</v>
+        <v>90569</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129084139</v>
       </c>
       <c r="B9" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129084136</v>
       </c>
       <c r="B11" t="n">
-        <v>92294</v>
+        <v>92301</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 49930-2025 artfynd.xlsx
+++ b/artfynd/A 49930-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129084141</v>
       </c>
       <c r="B2" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129084134</v>
       </c>
       <c r="B3" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129084140</v>
+        <v>129084129</v>
       </c>
       <c r="B4" t="n">
-        <v>56906</v>
+        <v>91506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>782641</v>
+        <v>782583</v>
       </c>
       <c r="R4" t="n">
-        <v>7291986</v>
+        <v>7291821</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129084129</v>
+        <v>129084140</v>
       </c>
       <c r="B5" t="n">
-        <v>91504</v>
+        <v>56908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>782583</v>
+        <v>782641</v>
       </c>
       <c r="R5" t="n">
-        <v>7291821</v>
+        <v>7291986</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129084138</v>
+        <v>129084143</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>82873</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>782588</v>
+        <v>782726</v>
       </c>
       <c r="R6" t="n">
-        <v>7291928</v>
+        <v>7292092</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129084143</v>
+        <v>129084138</v>
       </c>
       <c r="B7" t="n">
-        <v>82871</v>
+        <v>98678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782726</v>
+        <v>782588</v>
       </c>
       <c r="R7" t="n">
-        <v>7292092</v>
+        <v>7291928</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1260,7 +1260,7 @@
         <v>129084131</v>
       </c>
       <c r="B8" t="n">
-        <v>90569</v>
+        <v>90571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129084139</v>
       </c>
       <c r="B9" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129084142</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129084136</v>
       </c>
       <c r="B11" t="n">
-        <v>92301</v>
+        <v>92303</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 49930-2025 artfynd.xlsx
+++ b/artfynd/A 49930-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129084129</v>
+        <v>129084140</v>
       </c>
       <c r="B4" t="n">
-        <v>91506</v>
+        <v>56908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>782583</v>
+        <v>782641</v>
       </c>
       <c r="R4" t="n">
-        <v>7291821</v>
+        <v>7291986</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129084140</v>
+        <v>129084129</v>
       </c>
       <c r="B5" t="n">
-        <v>56908</v>
+        <v>91506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>782641</v>
+        <v>782583</v>
       </c>
       <c r="R5" t="n">
-        <v>7291986</v>
+        <v>7291821</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 49930-2025 artfynd.xlsx
+++ b/artfynd/A 49930-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129084141</v>
       </c>
       <c r="B2" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129084134</v>
       </c>
       <c r="B3" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129084129</v>
       </c>
       <c r="B5" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129084143</v>
+        <v>129084138</v>
       </c>
       <c r="B6" t="n">
-        <v>82873</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>782726</v>
+        <v>782588</v>
       </c>
       <c r="R6" t="n">
-        <v>7292092</v>
+        <v>7291928</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129084138</v>
+        <v>129084143</v>
       </c>
       <c r="B7" t="n">
-        <v>98678</v>
+        <v>82873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782588</v>
+        <v>782726</v>
       </c>
       <c r="R7" t="n">
-        <v>7291928</v>
+        <v>7292092</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1260,7 +1260,7 @@
         <v>129084131</v>
       </c>
       <c r="B8" t="n">
-        <v>90571</v>
+        <v>90572</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129084139</v>
       </c>
       <c r="B9" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129084136</v>
       </c>
       <c r="B11" t="n">
-        <v>92303</v>
+        <v>92317</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 49930-2025 artfynd.xlsx
+++ b/artfynd/A 49930-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129084141</v>
       </c>
       <c r="B2" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,14 +695,10 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -775,7 +771,7 @@
         <v>129084134</v>
       </c>
       <c r="B3" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +865,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129084140</v>
+        <v>129084129</v>
       </c>
       <c r="B4" t="n">
-        <v>56908</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +900,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>782641</v>
+        <v>782583</v>
       </c>
       <c r="R4" t="n">
-        <v>7291986</v>
+        <v>7291821</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +962,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129084129</v>
+        <v>129084140</v>
       </c>
       <c r="B5" t="n">
-        <v>91504</v>
+        <v>56908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +997,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>782583</v>
+        <v>782641</v>
       </c>
       <c r="R5" t="n">
-        <v>7291821</v>
+        <v>7291986</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,32 +1059,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129084138</v>
+        <v>129084143</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>82873</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1094,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>782588</v>
+        <v>782726</v>
       </c>
       <c r="R6" t="n">
-        <v>7291928</v>
+        <v>7292092</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,32 +1156,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129084143</v>
+        <v>129084138</v>
       </c>
       <c r="B7" t="n">
-        <v>82873</v>
+        <v>98705</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1191,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782726</v>
+        <v>782588</v>
       </c>
       <c r="R7" t="n">
-        <v>7292092</v>
+        <v>7291928</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1357,7 +1353,7 @@
         <v>129084139</v>
       </c>
       <c r="B9" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1547,7 @@
         <v>129084136</v>
       </c>
       <c r="B11" t="n">
-        <v>92317</v>
+        <v>92318</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 49930-2025 artfynd.xlsx
+++ b/artfynd/A 49930-2025 artfynd.xlsx
@@ -771,7 +771,7 @@
         <v>129084134</v>
       </c>
       <c r="B3" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129084129</v>
+        <v>129084140</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>56908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>782583</v>
+        <v>782641</v>
       </c>
       <c r="R4" t="n">
-        <v>7291821</v>
+        <v>7291986</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -962,32 +962,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129084140</v>
+        <v>129084129</v>
       </c>
       <c r="B5" t="n">
-        <v>56908</v>
+        <v>91504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>782641</v>
+        <v>782583</v>
       </c>
       <c r="R5" t="n">
-        <v>7291986</v>
+        <v>7291821</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1159,7 +1159,7 @@
         <v>129084138</v>
       </c>
       <c r="B7" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>129084139</v>
       </c>
       <c r="B9" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 49930-2025 artfynd.xlsx
+++ b/artfynd/A 49930-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129084141</v>
       </c>
       <c r="B2" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>129084134</v>
       </c>
       <c r="B3" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129084140</v>
+        <v>129084129</v>
       </c>
       <c r="B4" t="n">
-        <v>56908</v>
+        <v>91507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>782641</v>
+        <v>782583</v>
       </c>
       <c r="R4" t="n">
-        <v>7291986</v>
+        <v>7291821</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -962,32 +962,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129084129</v>
+        <v>129084140</v>
       </c>
       <c r="B5" t="n">
-        <v>91504</v>
+        <v>56908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>782583</v>
+        <v>782641</v>
       </c>
       <c r="R5" t="n">
-        <v>7291821</v>
+        <v>7291986</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1059,32 +1059,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129084143</v>
+        <v>129084138</v>
       </c>
       <c r="B6" t="n">
-        <v>82873</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>782726</v>
+        <v>782588</v>
       </c>
       <c r="R6" t="n">
-        <v>7292092</v>
+        <v>7291928</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1156,32 +1156,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129084138</v>
+        <v>129084143</v>
       </c>
       <c r="B7" t="n">
-        <v>98706</v>
+        <v>82877</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782588</v>
+        <v>782726</v>
       </c>
       <c r="R7" t="n">
-        <v>7291928</v>
+        <v>7292092</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1256,7 +1256,7 @@
         <v>129084131</v>
       </c>
       <c r="B8" t="n">
-        <v>90572</v>
+        <v>90575</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>129084139</v>
       </c>
       <c r="B9" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>129084142</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>129084136</v>
       </c>
       <c r="B11" t="n">
-        <v>92318</v>
+        <v>92321</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 49930-2025 artfynd.xlsx
+++ b/artfynd/A 49930-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129084141</v>
+        <v>129084143</v>
       </c>
       <c r="B2" t="n">
-        <v>91573</v>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>782753</v>
+        <v>782726</v>
       </c>
       <c r="R2" t="n">
-        <v>7292075</v>
+        <v>7292092</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -768,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129084134</v>
+        <v>129084136</v>
       </c>
       <c r="B3" t="n">
-        <v>97598</v>
+        <v>92692</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>1958</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -803,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>782585</v>
+        <v>782574</v>
       </c>
       <c r="R3" t="n">
-        <v>7291926</v>
+        <v>7291914</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129084129</v>
+        <v>129084131</v>
       </c>
       <c r="B4" t="n">
-        <v>91517</v>
+        <v>90932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -900,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>782583</v>
+        <v>782574</v>
       </c>
       <c r="R4" t="n">
-        <v>7291821</v>
+        <v>7291756</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -962,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129084140</v>
+        <v>129084129</v>
       </c>
       <c r="B5" t="n">
-        <v>56908</v>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -997,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>782641</v>
+        <v>782583</v>
       </c>
       <c r="R5" t="n">
-        <v>7291986</v>
+        <v>7291821</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1059,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129084138</v>
+        <v>129084133</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>93223</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5448</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1094,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>782588</v>
+        <v>782549</v>
       </c>
       <c r="R6" t="n">
-        <v>7291928</v>
+        <v>7291748</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1156,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129084143</v>
+        <v>129084135</v>
       </c>
       <c r="B7" t="n">
-        <v>82878</v>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1167,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1191,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782726</v>
+        <v>782601</v>
       </c>
       <c r="R7" t="n">
-        <v>7292092</v>
+        <v>7291748</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1253,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129084131</v>
+        <v>129084142</v>
       </c>
       <c r="B8" t="n">
-        <v>90585</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1288,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>782574</v>
+        <v>782593</v>
       </c>
       <c r="R8" t="n">
-        <v>7291756</v>
+        <v>7291880</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1350,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129084139</v>
+        <v>129084140</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>57132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1385,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>782604</v>
+        <v>782641</v>
       </c>
       <c r="R9" t="n">
-        <v>7291836</v>
+        <v>7291986</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1447,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129084142</v>
+        <v>129084138</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1482,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>782593</v>
+        <v>782588</v>
       </c>
       <c r="R10" t="n">
-        <v>7291880</v>
+        <v>7291928</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1544,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129084136</v>
+        <v>129084139</v>
       </c>
       <c r="B11" t="n">
-        <v>92331</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1555,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1958</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1579,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>782574</v>
+        <v>782604</v>
       </c>
       <c r="R11" t="n">
-        <v>7291914</v>
+        <v>7291836</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1638,6 +1642,103 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129084134</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Asplövberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>782585</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7291926</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49930-2025 artfynd.xlsx
+++ b/artfynd/A 49930-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129084143</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129084136</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129084131</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129084129</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129084133</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129084135</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129084142</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129084140</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129084138</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129084139</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,8 +1794,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129084134</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>